--- a/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 0,0</t>
+          <t>-11,2; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,24; 0,0</t>
+          <t>-11,34; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,22</t>
+          <t>0,0; 13,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 2,54</t>
+          <t>-5,73; 2,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 0,0</t>
+          <t>-7,09; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 0,94</t>
+          <t>-7,22; 1,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 0,8</t>
+          <t>-7,42; 1,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 6,4</t>
+          <t>-0,6; 6,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,64</t>
+          <t>-2,23; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 2,51</t>
+          <t>-2,91; 2,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 1,44</t>
+          <t>-4,02; 1,23</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-91,96; 61,73</t>
+          <t>-91,41; 96,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,37; 54,84</t>
+          <t>-91,85; 82,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,16; —</t>
+          <t>-63,8; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,06; 154,89</t>
+          <t>-63,98; 155,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,38; 90,55</t>
+          <t>-79,83; 100,77</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 4,15</t>
+          <t>-7,28; 5,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 0,0</t>
+          <t>-12,36; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,38; -1,82</t>
+          <t>-15,34; -1,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-13,09; 1,86</t>
+          <t>-11,51; 1,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 0,7</t>
+          <t>-8,83; 0,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,32; 0,09</t>
+          <t>-9,74; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 0,45</t>
+          <t>-5,9; 0,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 0,06</t>
+          <t>-6,52; -0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 3,44</t>
+          <t>-2,21; 3,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,38</t>
+          <t>-3,15; 2,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,35</t>
+          <t>-3,22; 1,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,25</t>
+          <t>-3,83; 0,25</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-87,28; 40,28</t>
+          <t>-90,45; 37,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-91,77; 34,91</t>
+          <t>-92,46; 5,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 361,95</t>
+          <t>-63,66; 419,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,44; 312,67</t>
+          <t>-85,1; 259,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,5; 69,07</t>
+          <t>-67,15; 65,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,79; 23,99</t>
+          <t>-81,21; 24,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 0,0</t>
+          <t>-12,28; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 0,0</t>
+          <t>-12,46; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,89</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -651,12 +651,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 2,51</t>
+          <t>-4,32; 3,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 0,0</t>
+          <t>-7,83; 0,0</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,37</t>
+          <t>-7,73; 1,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 1,07</t>
+          <t>-7,97; 0,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 6,55</t>
+          <t>-0,87; 6,57</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,2</t>
+          <t>-2,25; 3,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 2,66</t>
+          <t>-2,66; 2,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,23</t>
+          <t>-3,75; 1,43</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-91,41; 96,0</t>
+          <t>-92,5; 82,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-91,85; 82,42</t>
+          <t>-93,25; 46,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,8; —</t>
+          <t>-74,65; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,98; 155,26</t>
+          <t>-58,62; 173,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-79,83; 100,77</t>
+          <t>-78,96; 95,73</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 5,79</t>
+          <t>-7,09; 4,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 0,0</t>
+          <t>-11,82; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -1,83</t>
+          <t>-13,72; -1,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,51; 1,93</t>
+          <t>-11,52; 1,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 0,94</t>
+          <t>-9,12; 0,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,0</t>
+          <t>-8,85; 0,01</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 0,48</t>
+          <t>-5,82; 0,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; -0,37</t>
+          <t>-6,33; -0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 3,5</t>
+          <t>-2,36; 3,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,34</t>
+          <t>-3,18; 2,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,19</t>
+          <t>-2,94; 1,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,25</t>
+          <t>-3,54; 0,24</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-90,45; 37,26</t>
+          <t>-88,98; 41,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,46; 5,9</t>
+          <t>-92,51; 23,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,66; 419,81</t>
+          <t>-69,22; 393,33</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,1; 259,71</t>
+          <t>-85,23; 322,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-67,15; 65,52</t>
+          <t>-65,81; 78,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,21; 24,63</t>
+          <t>-81,06; 24,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
@@ -513,19 +513,19 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-2,71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-2,71</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 0,0</t>
+          <t>0,0; 12,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,46; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>-13,7; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,24; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 3,65</t>
+          <t>-4,47; 2,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 0,0</t>
+          <t>-7,16; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,56</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,68</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-2,85</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>-2,91</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 1,05</t>
+          <t>-0,86; 6,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 0,69</t>
+          <t>-2,24; 3,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,57</t>
+          <t>-7,51; 0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 3,62</t>
+          <t>-7,28; 0,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,75</t>
+          <t>-3,28; 2,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,43</t>
+          <t>-3,86; 1,44</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>174,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46,09%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-56,27%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>-57,51%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>174,15%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,5; 82,98</t>
+          <t>-63,16; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-93,25; 46,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-74,65; —</t>
+          <t>-91,96; 61,73</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-91,37; 54,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,62; 173,79</t>
+          <t>-66,06; 154,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 95,73</t>
+          <t>-78,38; 90,55</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-5,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-3,76</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,23</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-2,29</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-5,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-3,76</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 4,2</t>
+          <t>-15,38; -1,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 0,0</t>
+          <t>-13,09; 1,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-13,72; -1,81</t>
+          <t>-7,18; 4,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 1,92</t>
+          <t>-11,34; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 0,1</t>
+          <t>-8,96; 0,7</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 0,01</t>
+          <t>-9,32; 0,09</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-66,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-10,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-66,95%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-2,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>-2,75</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 0,44</t>
+          <t>-2,11; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; -0,15</t>
+          <t>-3,18; 2,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 3,15</t>
+          <t>-5,45; 0,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,36</t>
+          <t>-6,23; 0,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,41</t>
+          <t>-2,99; 1,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 0,24</t>
+          <t>-3,52; 0,25</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27,58%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-17,32%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-54,86%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>-66,23%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-17,32%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 41,58</t>
+          <t>-62,7; 361,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-92,51; 23,97</t>
+          <t>-85,44; 312,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 393,33</t>
+          <t>-87,28; 40,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-85,23; 322,87</t>
+          <t>-91,77; 34,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 78,3</t>
+          <t>-67,5; 69,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,06; 24,22</t>
+          <t>-81,79; 23,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP16A09-Estudios-trans_camb.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -118,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -131,6 +134,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -497,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -591,467 +600,285 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,66</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,71</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.7092397263353969</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-0.6575641967672962</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.6575641967672962</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.005799523793262882</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-0.3362243742516457</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 12,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-13,7; 0,0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-12,24; 0,0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-4,47; 2,54</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-7,16; 0,0</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="n">
+        <v>-3.38647705651593</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-3.402184969232204</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-0.6747019561740966</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-1.692106869097121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-11,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.605039556038978</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>1.352648150838536</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.01724896895464888</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Secundarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,56</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,68</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-0,86; 6,4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-2,24; 3,64</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-7,51; 0,94</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,28; 0,8</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 2,51</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-3,86; 1,44</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n"/>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>174,15%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>46,09%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-56,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-57,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,21%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-32,64%</t>
-        </is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7359309831072043</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.1591650110686951</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.4156191421585029</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.4991370437732469</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.1942251004076715</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.1461973965731732</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-63,16; —</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-91,96; 61,73</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-91,37; 54,84</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-66,06; 154,89</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-78,38; 90,55</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.001654755235716862</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.394709863642123</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-1.425746063585179</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.459738204491535</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-0.3680166541276696</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-0.6632862007518902</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Cambio absoluto (puntos porcentuales)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,62</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,76</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,23</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,29</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,29</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1.669571242903229</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.855758053379042</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.4353720568895688</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.2378346831912628</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.8382973211409372</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.3865942548266619</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-15,38; -1,82</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-13,09; 1,86</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,18; 4,15</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-11,34; 0,0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,96; 0,7</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-9,32; 0,09</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2.722395624998835</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0.5887918021290669</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.4235920209998437</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.508712057942617</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.3228942096941714</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2430493933418277</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-66,95%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-10,25%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-76,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-78,55%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-0.6342743461079978</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="n">
+        <v>-0.8888615521214945</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.8996244543061931</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5218976173400276</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7607505517042524</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr"/>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="n">
+        <v>1.316876629850149</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.7659052163502235</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>2.386532099709499</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>1.116900591196743</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1059,153 +886,293 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>0,63</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-0,4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,28</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,75</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,52</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-1.253846507712669</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.8806690369416774</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.2686465308903581</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.2969843465118555</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.4729423208135165</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.5582248432936235</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-2,11; 3,44</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 2,38</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-5,45; 0,45</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-6,23; 0,06</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-2,99; 1,35</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-3,52; 0,25</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.552000427122341</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.980661025645619</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.5931139855822739</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.518410440253965</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-1.498934526377171</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-1.537521007112124</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Cambio relativo (%)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>27,58%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-17,32%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-54,86%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-66,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-23,91%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-48,21%</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-0.4081595078502146</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.3322047282471685</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.465358401139211</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.4504213203055019</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.1860509564044626</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>-62,7; 361,95</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>-85,44; 312,67</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>-87,28; 40,28</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>-91,77; 34,91</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>-67,5; 69,07</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>-81,79; 23,99</t>
-        </is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-0.7023738803150947</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.904581450321099</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.6285145565553278</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.7418503787890067</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Cambio absoluto (puntos porcentuales)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.2903309399495292</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.07748428212613427</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.2706469839106184</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.4399068116604758</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.01778730558488874</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.2534392464120709</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.3353706361975479</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-0.6215950403097731</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.9380025077117975</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-1.148665229723314</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-0.4827276700170768</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-0.6646266090201747</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.012092376219196</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4811707869473137</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3771390971929681</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.08246186853890851</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.4612606088470217</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>0.103080652282127</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Cambio relativo (%)</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>0.6405750704941054</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1709583535732086</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.3546577476050812</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.5764570390747887</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.0294659872307346</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.4198408557667894</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>-0.6140362283582117</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.8510975685879885</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.8597191290788384</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.915666159977949</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5996055590822987</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.8005795567816436</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>4.487773722677509</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>2.683673489649151</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>1.154606939313844</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.5563289563199708</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>1.103078021425621</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.3985772728165204</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1213,14 +1180,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A22:A27"/>
+    <mergeCell ref="A4:A9"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A16:A21"/>
+    <mergeCell ref="A10:A15"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
